--- a/Table.xlsx
+++ b/Table.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Kuliah\Louise\Login FInite State Machine\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE5FD11E-95D2-4F7B-BA7B-E98789590CDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA1C55A2-85A2-4950-84D8-6A8DF996D046}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4DF15EA3-3207-4464-9798-70FC224B1705}"/>
   </bookViews>
@@ -187,7 +187,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -210,26 +210,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFC4C7C5"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFC4C7C5"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFC4C7C5"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFC4C7C5"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
@@ -240,14 +225,15 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -563,7 +549,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DAB4A7A-86D1-4961-A150-C7415A69C6CC}">
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26" bestFit="1" customWidth="1"/>
@@ -578,34 +564,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6" t="s">
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="6"/>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
+      <c r="A2" s="4"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
       <c r="D2" s="1" t="s">
         <v>35</v>
       </c>
@@ -615,9 +601,9 @@
       <c r="F2" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -909,105 +895,122 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="14" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="4"/>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
-    </row>
-    <row r="15" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="4"/>
-      <c r="B15" s="5"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="5"/>
-    </row>
-    <row r="16" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="4"/>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="4"/>
-      <c r="G16" s="5"/>
-    </row>
-    <row r="17" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="4"/>
-      <c r="B17" s="5"/>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="4"/>
-      <c r="G17" s="5"/>
-    </row>
-    <row r="18" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="4"/>
-      <c r="B18" s="5"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="4"/>
-      <c r="G18" s="5"/>
-    </row>
-    <row r="19" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="4"/>
-      <c r="B19" s="5"/>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="4"/>
-      <c r="G19" s="5"/>
-    </row>
-    <row r="20" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="4"/>
-      <c r="B20" s="5"/>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="4"/>
-      <c r="G20" s="5"/>
-    </row>
-    <row r="21" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="4"/>
-      <c r="B21" s="5"/>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="4"/>
-      <c r="G21" s="5"/>
-    </row>
-    <row r="22" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="4"/>
-      <c r="B22" s="5"/>
-      <c r="C22" s="5"/>
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="4"/>
-      <c r="G22" s="5"/>
-    </row>
-    <row r="23" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="4"/>
-      <c r="B23" s="5"/>
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="4"/>
-      <c r="G23" s="5"/>
-    </row>
-    <row r="24" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="4"/>
-      <c r="B24" s="5"/>
-      <c r="C24" s="5"/>
-      <c r="D24" s="5"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="4"/>
-      <c r="G24" s="5"/>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="5"/>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="6"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" s="6"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="7"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" s="6"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="7"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="6"/>
+      <c r="B17" s="7"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="7"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="6"/>
+      <c r="B18" s="7"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="7"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="6"/>
+      <c r="B19" s="7"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="6"/>
+      <c r="G19" s="7"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="6"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="7"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="6"/>
+      <c r="B21" s="7"/>
+      <c r="C21" s="7"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="6"/>
+      <c r="G21" s="7"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="6"/>
+      <c r="B22" s="7"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="6"/>
+      <c r="G22" s="7"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="6"/>
+      <c r="B23" s="7"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="6"/>
+      <c r="G23" s="7"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="6"/>
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="6"/>
+      <c r="G24" s="7"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="5"/>
+      <c r="B25" s="5"/>
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="7">
